--- a/app/views/mission/report.xlsx
+++ b/app/views/mission/report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MBF_CODE\nq57-catp\app\views\mission\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4A8B17B-89B6-4BEF-9A4B-A8E375F2FAD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB0724A-0FBD-41FC-9B9C-4D9C75263012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{39A18495-5D43-46ED-9E40-188D831473E2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>BÁO CÁO KẾT QUẢ THỰC HIỆN NHIỆM VỤ</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>Đơn vị chủ trì</t>
+  </si>
+  <si>
+    <t>Ngày bắt đầu</t>
   </si>
 </sst>
 </file>
@@ -517,20 +520,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D489503-7789-406A-BB7E-537AD43169FC}">
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="9" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="33.75" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:23" ht="33.75" x14ac:dyDescent="0.5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -552,11 +556,12 @@
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
-      <c r="T1" s="8"/>
+      <c r="T1" s="1"/>
       <c r="U1" s="8"/>
-      <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="V1" s="8"/>
+      <c r="W1" s="1"/>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="3" t="s">
         <v>6</v>
@@ -577,11 +582,12 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
-      <c r="T2" s="8"/>
+      <c r="T2" s="1"/>
       <c r="U2" s="8"/>
-      <c r="V2" s="1"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="V2" s="8"/>
+      <c r="W2" s="1"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="3" t="s">
         <v>2</v>
@@ -602,11 +608,12 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
-      <c r="T3" s="8"/>
+      <c r="T3" s="1"/>
       <c r="U3" s="8"/>
-      <c r="V3" s="1"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="V3" s="8"/>
+      <c r="W3" s="1"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="7" t="s">
         <v>12</v>
@@ -627,11 +634,12 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
-      <c r="T4" s="8"/>
+      <c r="T4" s="1"/>
       <c r="U4" s="8"/>
-      <c r="V4" s="1"/>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="V4" s="8"/>
+      <c r="W4" s="1"/>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="3" t="s">
         <v>13</v>
@@ -652,11 +660,12 @@
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
-      <c r="T5" s="8"/>
+      <c r="T5" s="1"/>
       <c r="U5" s="8"/>
-      <c r="V5" s="1"/>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="V5" s="8"/>
+      <c r="W5" s="1"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="3" t="s">
         <v>14</v>
@@ -677,11 +686,12 @@
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
-      <c r="T6" s="8"/>
+      <c r="T6" s="1"/>
       <c r="U6" s="8"/>
-      <c r="V6" s="1"/>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="V6" s="8"/>
+      <c r="W6" s="1"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="3" t="s">
         <v>4</v>
@@ -702,11 +712,12 @@
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
-      <c r="T7" s="8"/>
+      <c r="T7" s="1"/>
       <c r="U7" s="8"/>
-      <c r="V7" s="1"/>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="V7" s="8"/>
+      <c r="W7" s="1"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="3" t="s">
         <v>5</v>
@@ -726,14 +737,15 @@
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
-      <c r="T8" s="8"/>
+      <c r="T8" s="1"/>
       <c r="U8" s="8"/>
-      <c r="V8" s="1"/>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="V8" s="8"/>
+      <c r="W8" s="1"/>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>7</v>
       </c>
@@ -782,35 +794,38 @@
       <c r="P10" s="6">
         <v>46034</v>
       </c>
-      <c r="Q10" s="5" t="s">
+      <c r="Q10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="R10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="R10" s="5" t="s">
+      <c r="S10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="S10" s="5" t="s">
+      <c r="T10" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="T10" s="5" t="s">
+      <c r="U10" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="U10" s="5" t="s">
+      <c r="V10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="V10" s="5" t="s">
+      <c r="W10" s="5" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="U7:V7"/>
+    <mergeCell ref="U8:V8"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="U4:V4"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="U6:V6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
